--- a/data/novedades/Inactivos_posgrado.xlsx
+++ b/data/novedades/Inactivos_posgrado.xlsx
@@ -16,11 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +49,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2578,10 +2575,8 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>1102</t>
-        </is>
+      <c r="A23" t="n">
+        <v>1102</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -2633,7 +2628,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N23" s="2" t="n">
+      <c r="N23" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O23" t="inlineStr">
@@ -2678,10 +2673,8 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>1102</t>
-        </is>
+      <c r="A24" t="n">
+        <v>1102</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -2733,7 +2726,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N24" s="2" t="n">
+      <c r="N24" s="1" t="n">
         <v>37572</v>
       </c>
       <c r="O24" t="inlineStr">
@@ -2778,10 +2771,8 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>1106</t>
-        </is>
+      <c r="A25" t="n">
+        <v>1106</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -2835,7 +2826,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N25" s="2" t="n">
+      <c r="N25" s="1" t="n">
         <v>43522</v>
       </c>
       <c r="O25" t="inlineStr">
@@ -2880,10 +2871,8 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A26" t="n">
+        <v>1110</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -2935,7 +2924,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N26" s="2" t="n">
+      <c r="N26" s="1" t="n">
         <v>42003</v>
       </c>
       <c r="O26" t="inlineStr">
@@ -2980,10 +2969,8 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A27" t="n">
+        <v>1110</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -3035,7 +3022,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N27" s="2" t="n">
+      <c r="N27" s="1" t="n">
         <v>42240</v>
       </c>
       <c r="O27" t="inlineStr">
@@ -3080,10 +3067,8 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A28" t="n">
+        <v>1110</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -3135,7 +3120,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N28" s="2" t="n">
+      <c r="N28" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O28" t="inlineStr">
@@ -3180,10 +3165,8 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A29" t="n">
+        <v>1110</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -3235,7 +3218,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N29" s="2" t="n">
+      <c r="N29" s="1" t="n">
         <v>36564</v>
       </c>
       <c r="O29" t="inlineStr">
@@ -3280,10 +3263,8 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A30" t="n">
+        <v>1110</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -3335,7 +3316,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N30" s="2" t="n">
+      <c r="N30" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O30" t="inlineStr">
@@ -3380,10 +3361,8 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A31" t="n">
+        <v>1110</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -3435,7 +3414,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N31" s="2" t="n">
+      <c r="N31" s="1" t="n">
         <v>41799</v>
       </c>
       <c r="O31" t="inlineStr">
@@ -3480,10 +3459,8 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A32" t="n">
+        <v>1110</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -3535,7 +3512,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N32" s="2" t="n">
+      <c r="N32" s="1" t="n">
         <v>43112</v>
       </c>
       <c r="O32" t="inlineStr">
@@ -3580,10 +3557,8 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A33" t="n">
+        <v>1110</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -3635,7 +3610,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N33" s="2" t="n">
+      <c r="N33" s="1" t="n">
         <v>41747</v>
       </c>
       <c r="O33" t="inlineStr">
@@ -3680,10 +3655,8 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A34" t="n">
+        <v>1110</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -3735,7 +3708,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N34" s="2" t="n">
+      <c r="N34" s="1" t="n">
         <v>39146</v>
       </c>
       <c r="O34" t="inlineStr">
@@ -3780,10 +3753,8 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A35" t="n">
+        <v>1110</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -3835,7 +3806,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N35" s="2" t="n">
+      <c r="N35" s="1" t="n">
         <v>42466</v>
       </c>
       <c r="O35" t="inlineStr">
@@ -3880,10 +3851,8 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A36" t="n">
+        <v>1110</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -3935,7 +3904,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N36" s="2" t="n">
+      <c r="N36" s="1" t="n">
         <v>36438</v>
       </c>
       <c r="O36" t="inlineStr">
@@ -3980,10 +3949,8 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A37" t="n">
+        <v>1110</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -4035,7 +4002,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N37" s="2" t="n">
+      <c r="N37" s="1" t="n">
         <v>42275</v>
       </c>
       <c r="O37" t="inlineStr">
@@ -4080,10 +4047,8 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A38" t="n">
+        <v>1110</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -4135,7 +4100,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N38" s="2" t="n">
+      <c r="N38" s="1" t="n">
         <v>41935</v>
       </c>
       <c r="O38" t="inlineStr">
@@ -4180,10 +4145,8 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A39" t="n">
+        <v>1110</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -4235,7 +4198,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N39" s="2" t="n">
+      <c r="N39" s="1" t="n">
         <v>41810</v>
       </c>
       <c r="O39" t="inlineStr">
@@ -4280,10 +4243,8 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A40" t="n">
+        <v>1110</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -4335,7 +4296,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N40" s="2" t="n">
+      <c r="N40" s="1" t="n">
         <v>42195</v>
       </c>
       <c r="O40" t="inlineStr">
@@ -4380,10 +4341,8 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A41" t="n">
+        <v>1110</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -4435,7 +4394,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N41" s="2" t="n">
+      <c r="N41" s="1" t="n">
         <v>42208</v>
       </c>
       <c r="O41" t="inlineStr">
@@ -4480,10 +4439,8 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A42" t="n">
+        <v>1110</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -4535,7 +4492,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N42" s="2" t="n">
+      <c r="N42" s="1" t="n">
         <v>37809</v>
       </c>
       <c r="O42" t="inlineStr">
@@ -4580,10 +4537,8 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A43" t="n">
+        <v>1110</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -4635,7 +4590,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N43" s="2" t="n">
+      <c r="N43" s="1" t="n">
         <v>42753</v>
       </c>
       <c r="O43" t="inlineStr">
@@ -4680,10 +4635,8 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A44" t="n">
+        <v>1110</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -4735,7 +4688,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N44" s="2" t="n">
+      <c r="N44" s="1" t="n">
         <v>42811</v>
       </c>
       <c r="O44" t="inlineStr">
@@ -4780,10 +4733,8 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A45" t="n">
+        <v>1110</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -4835,7 +4786,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N45" s="2" t="n">
+      <c r="N45" s="1" t="n">
         <v>42109</v>
       </c>
       <c r="O45" t="inlineStr">
@@ -4880,10 +4831,8 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A46" t="n">
+        <v>1110</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -4935,7 +4884,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N46" s="2" t="n">
+      <c r="N46" s="1" t="n">
         <v>42510</v>
       </c>
       <c r="O46" t="inlineStr">
@@ -4980,10 +4929,8 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A47" t="n">
+        <v>1110</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -5035,7 +4982,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N47" s="2" t="n">
+      <c r="N47" s="1" t="n">
         <v>42041</v>
       </c>
       <c r="O47" t="inlineStr">
@@ -5080,10 +5027,8 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A48" t="n">
+        <v>1110</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -5135,7 +5080,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N48" s="2" t="n">
+      <c r="N48" s="1" t="n">
         <v>42080</v>
       </c>
       <c r="O48" t="inlineStr">
@@ -5180,10 +5125,8 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A49" t="n">
+        <v>1110</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -5235,7 +5178,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N49" s="2" t="n">
+      <c r="N49" s="1" t="n">
         <v>41404</v>
       </c>
       <c r="O49" t="inlineStr">
@@ -5280,10 +5223,8 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A50" t="n">
+        <v>1110</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -5335,7 +5276,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N50" s="2" t="n">
+      <c r="N50" s="1" t="n">
         <v>42012</v>
       </c>
       <c r="O50" t="inlineStr">
@@ -5380,10 +5321,8 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A51" t="n">
+        <v>1110</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -5435,7 +5374,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N51" s="2" t="n">
+      <c r="N51" s="1" t="n">
         <v>41847</v>
       </c>
       <c r="O51" t="inlineStr">
@@ -5480,10 +5419,8 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A52" t="n">
+        <v>1110</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -5535,7 +5472,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N52" s="2" t="n">
+      <c r="N52" s="1" t="n">
         <v>42405</v>
       </c>
       <c r="O52" t="inlineStr">
@@ -5580,10 +5517,8 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A53" t="n">
+        <v>1110</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -5635,7 +5570,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N53" s="2" t="n">
+      <c r="N53" s="1" t="n">
         <v>42365</v>
       </c>
       <c r="O53" t="inlineStr">
@@ -5680,10 +5615,8 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A54" t="n">
+        <v>1110</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -5735,7 +5668,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N54" s="2" t="n">
+      <c r="N54" s="1" t="n">
         <v>42145</v>
       </c>
       <c r="O54" t="inlineStr">
@@ -5780,10 +5713,8 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A55" t="n">
+        <v>1110</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -5835,7 +5766,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N55" s="2" t="n">
+      <c r="N55" s="1" t="n">
         <v>42213</v>
       </c>
       <c r="O55" t="inlineStr">
@@ -5880,10 +5811,8 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A56" t="n">
+        <v>1110</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -5935,7 +5864,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N56" s="2" t="n">
+      <c r="N56" s="1" t="n">
         <v>42145</v>
       </c>
       <c r="O56" t="inlineStr">
@@ -5980,10 +5909,8 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A57" t="n">
+        <v>1110</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -6035,7 +5962,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N57" s="2" t="n">
+      <c r="N57" s="1" t="n">
         <v>42405</v>
       </c>
       <c r="O57" t="inlineStr">
@@ -6080,10 +6007,8 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A58" t="n">
+        <v>1110</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -6135,7 +6060,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N58" s="2" t="n">
+      <c r="N58" s="1" t="n">
         <v>42145</v>
       </c>
       <c r="O58" t="inlineStr">
@@ -6180,10 +6105,8 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A59" t="n">
+        <v>1110</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -6235,7 +6158,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N59" s="2" t="n">
+      <c r="N59" s="1" t="n">
         <v>42405</v>
       </c>
       <c r="O59" t="inlineStr">
@@ -6280,10 +6203,8 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A60" t="n">
+        <v>1110</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -6335,7 +6256,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N60" s="2" t="n">
+      <c r="N60" s="1" t="n">
         <v>42405</v>
       </c>
       <c r="O60" t="inlineStr">
@@ -6380,10 +6301,8 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A61" t="n">
+        <v>1110</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -6435,7 +6354,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N61" s="2" t="n">
+      <c r="N61" s="1" t="n">
         <v>42145</v>
       </c>
       <c r="O61" t="inlineStr">
@@ -6480,10 +6399,8 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A62" t="n">
+        <v>1110</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -6535,7 +6452,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N62" s="2" t="n">
+      <c r="N62" s="1" t="n">
         <v>42466</v>
       </c>
       <c r="O62" t="inlineStr">
@@ -6580,10 +6497,8 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A63" t="n">
+        <v>1110</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -6635,7 +6550,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N63" s="2" t="n">
+      <c r="N63" s="1" t="n">
         <v>42165</v>
       </c>
       <c r="O63" t="inlineStr">
@@ -6680,10 +6595,8 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A64" t="n">
+        <v>1110</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -6735,7 +6648,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N64" s="2" t="n">
+      <c r="N64" s="1" t="n">
         <v>41939</v>
       </c>
       <c r="O64" t="inlineStr">
@@ -6780,10 +6693,8 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A65" t="n">
+        <v>1110</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -6835,7 +6746,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N65" s="2" t="n">
+      <c r="N65" s="1" t="n">
         <v>40408</v>
       </c>
       <c r="O65" t="inlineStr">
@@ -6880,10 +6791,8 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A66" t="n">
+        <v>1110</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -6935,7 +6844,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N66" s="2" t="n">
+      <c r="N66" s="1" t="n">
         <v>41842</v>
       </c>
       <c r="O66" t="inlineStr">
@@ -6980,10 +6889,8 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A67" t="n">
+        <v>1110</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -7035,7 +6942,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N67" s="2" t="n">
+      <c r="N67" s="1" t="n">
         <v>42511</v>
       </c>
       <c r="O67" t="inlineStr">
@@ -7080,10 +6987,8 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A68" t="n">
+        <v>1110</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -7135,7 +7040,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N68" s="2" t="n">
+      <c r="N68" s="1" t="n">
         <v>42404</v>
       </c>
       <c r="O68" t="inlineStr">
@@ -7180,10 +7085,8 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A69" t="n">
+        <v>1110</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -7235,7 +7138,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N69" s="2" t="n">
+      <c r="N69" s="1" t="n">
         <v>40408</v>
       </c>
       <c r="O69" t="inlineStr">
@@ -7280,10 +7183,8 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A70" t="n">
+        <v>1110</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -7335,7 +7236,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N70" s="2" t="n">
+      <c r="N70" s="1" t="n">
         <v>42145</v>
       </c>
       <c r="O70" t="inlineStr">
@@ -7380,10 +7281,8 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>1110</t>
-        </is>
+      <c r="A71" t="n">
+        <v>1110</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -7435,7 +7334,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N71" s="2" t="n">
+      <c r="N71" s="1" t="n">
         <v>42195</v>
       </c>
       <c r="O71" t="inlineStr">
@@ -7480,10 +7379,8 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>1115</t>
-        </is>
+      <c r="A72" t="n">
+        <v>1115</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -7535,7 +7432,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N72" s="2" t="n">
+      <c r="N72" s="1" t="n">
         <v>43003</v>
       </c>
       <c r="O72" t="inlineStr">
@@ -7580,10 +7477,8 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>1115</t>
-        </is>
+      <c r="A73" t="n">
+        <v>1115</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -7635,7 +7530,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N73" s="2" t="n">
+      <c r="N73" s="1" t="n">
         <v>42959</v>
       </c>
       <c r="O73" t="inlineStr">
@@ -7680,10 +7575,8 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>1115</t>
-        </is>
+      <c r="A74" t="n">
+        <v>1115</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -7735,7 +7628,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N74" s="2" t="n">
+      <c r="N74" s="1" t="n">
         <v>42802</v>
       </c>
       <c r="O74" t="inlineStr">
@@ -7780,10 +7673,8 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>1117</t>
-        </is>
+      <c r="A75" t="n">
+        <v>1117</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -7837,7 +7728,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N75" s="2" t="n">
+      <c r="N75" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O75" t="inlineStr">
@@ -7882,10 +7773,8 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>1201</t>
-        </is>
+      <c r="A76" t="n">
+        <v>1201</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -7939,7 +7828,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N76" s="2" t="n">
+      <c r="N76" s="1" t="n">
         <v>43584</v>
       </c>
       <c r="O76" t="inlineStr">
@@ -7984,10 +7873,8 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>1203</t>
-        </is>
+      <c r="A77" t="n">
+        <v>1203</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -8039,7 +7926,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N77" s="2" t="n">
+      <c r="N77" s="1" t="n">
         <v>36416</v>
       </c>
       <c r="O77" t="inlineStr">
@@ -8084,10 +7971,8 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>1203</t>
-        </is>
+      <c r="A78" t="n">
+        <v>1203</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -8139,7 +8024,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N78" s="2" t="n">
+      <c r="N78" s="1" t="n">
         <v>39749</v>
       </c>
       <c r="O78" t="inlineStr">
@@ -8184,10 +8069,8 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>1203</t>
-        </is>
+      <c r="A79" t="n">
+        <v>1203</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -8239,7 +8122,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N79" s="2" t="n">
+      <c r="N79" s="1" t="n">
         <v>43846</v>
       </c>
       <c r="O79" t="inlineStr">
@@ -8284,10 +8167,8 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>1203</t>
-        </is>
+      <c r="A80" t="n">
+        <v>1203</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -8341,7 +8222,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N80" s="2" t="n">
+      <c r="N80" s="1" t="n">
         <v>40498</v>
       </c>
       <c r="O80" t="inlineStr">
@@ -8386,10 +8267,8 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>1203</t>
-        </is>
+      <c r="A81" t="n">
+        <v>1203</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
@@ -8441,7 +8320,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N81" s="2" t="n">
+      <c r="N81" s="1" t="n">
         <v>45484</v>
       </c>
       <c r="O81" t="inlineStr">
@@ -8486,10 +8365,8 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>1203</t>
-        </is>
+      <c r="A82" t="n">
+        <v>1203</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
@@ -8541,7 +8418,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N82" s="2" t="n">
+      <c r="N82" s="1" t="n">
         <v>43363</v>
       </c>
       <c r="O82" t="inlineStr">
@@ -8586,10 +8463,8 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>1206</t>
-        </is>
+      <c r="A83" t="n">
+        <v>1206</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
@@ -8643,7 +8518,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N83" s="2" t="n">
+      <c r="N83" s="1" t="n">
         <v>43679</v>
       </c>
       <c r="O83" t="inlineStr">
@@ -8688,10 +8563,8 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>1213</t>
-        </is>
+      <c r="A84" t="n">
+        <v>1213</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
@@ -8743,7 +8616,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N84" s="2" t="n">
+      <c r="N84" s="1" t="n">
         <v>43163</v>
       </c>
       <c r="O84" t="inlineStr">
@@ -8788,10 +8661,8 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>1213</t>
-        </is>
+      <c r="A85" t="n">
+        <v>1213</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
@@ -8845,7 +8716,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N85" s="2" t="n">
+      <c r="N85" s="1" t="n">
         <v>43216</v>
       </c>
       <c r="O85" t="inlineStr">
@@ -8890,10 +8761,8 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>1213</t>
-        </is>
+      <c r="A86" t="n">
+        <v>1213</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
@@ -8945,7 +8814,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N86" s="2" t="n">
+      <c r="N86" s="1" t="n">
         <v>43163</v>
       </c>
       <c r="O86" t="inlineStr">
@@ -8990,10 +8859,8 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>1213</t>
-        </is>
+      <c r="A87" t="n">
+        <v>1213</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
@@ -9047,7 +8914,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N87" s="2" t="n">
+      <c r="N87" s="1" t="n">
         <v>43216</v>
       </c>
       <c r="O87" t="inlineStr">
@@ -9092,10 +8959,8 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
+      <c r="A88" t="n">
+        <v>1701</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
@@ -9149,7 +9014,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N88" s="2" t="n">
+      <c r="N88" s="1" t="n">
         <v>39132</v>
       </c>
       <c r="O88" t="inlineStr">
@@ -9194,10 +9059,8 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
+      <c r="A89" t="n">
+        <v>1701</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
@@ -9249,7 +9112,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N89" s="2" t="n">
+      <c r="N89" s="1" t="n">
         <v>42701</v>
       </c>
       <c r="O89" t="inlineStr">
@@ -9294,10 +9157,8 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
+      <c r="A90" t="n">
+        <v>1701</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
@@ -9349,7 +9210,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N90" s="2" t="n">
+      <c r="N90" s="1" t="n">
         <v>42290</v>
       </c>
       <c r="O90" t="inlineStr">
@@ -9394,10 +9255,8 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
+      <c r="A91" t="n">
+        <v>1701</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
@@ -9451,7 +9310,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N91" s="2" t="n">
+      <c r="N91" s="1" t="n">
         <v>43500</v>
       </c>
       <c r="O91" t="inlineStr">
@@ -9496,10 +9355,8 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
+      <c r="A92" t="n">
+        <v>1701</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
@@ -9551,7 +9408,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N92" s="2" t="n">
+      <c r="N92" s="1" t="n">
         <v>42999</v>
       </c>
       <c r="O92" t="inlineStr">
@@ -9596,10 +9453,8 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
+      <c r="A93" t="n">
+        <v>1701</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
@@ -9653,7 +9508,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N93" s="2" t="n">
+      <c r="N93" s="1" t="n">
         <v>42240</v>
       </c>
       <c r="O93" t="inlineStr">
@@ -9698,10 +9553,8 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>1702</t>
-        </is>
+      <c r="A94" t="n">
+        <v>1702</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
@@ -9753,7 +9606,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N94" s="2" t="n">
+      <c r="N94" s="1" t="n">
         <v>45811</v>
       </c>
       <c r="O94" t="inlineStr">
@@ -9798,10 +9651,8 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>1710</t>
-        </is>
+      <c r="A95" t="n">
+        <v>1710</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
@@ -9855,7 +9706,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N95" s="2" t="n">
+      <c r="N95" s="1" t="n">
         <v>43326</v>
       </c>
       <c r="O95" t="inlineStr">
@@ -9900,10 +9751,8 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>1711</t>
-        </is>
+      <c r="A96" t="n">
+        <v>1711</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
@@ -9957,7 +9806,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N96" s="2" t="n">
+      <c r="N96" s="1" t="n">
         <v>43220</v>
       </c>
       <c r="O96" t="inlineStr">
@@ -10002,10 +9851,8 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>1713</t>
-        </is>
+      <c r="A97" t="n">
+        <v>1713</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
@@ -10057,7 +9904,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N97" s="2" t="n">
+      <c r="N97" s="1" t="n">
         <v>43095</v>
       </c>
       <c r="O97" t="inlineStr">
@@ -10102,10 +9949,8 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>1713</t>
-        </is>
+      <c r="A98" t="n">
+        <v>1713</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
@@ -10157,7 +10002,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N98" s="2" t="n">
+      <c r="N98" s="1" t="n">
         <v>43327</v>
       </c>
       <c r="O98" t="inlineStr">
@@ -10202,10 +10047,8 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>1713</t>
-        </is>
+      <c r="A99" t="n">
+        <v>1713</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
@@ -10257,7 +10100,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N99" s="2" t="n">
+      <c r="N99" s="1" t="n">
         <v>42927</v>
       </c>
       <c r="O99" t="inlineStr">
@@ -10302,10 +10145,8 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
+      <c r="A100" t="n">
+        <v>1714</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
@@ -10359,7 +10200,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N100" s="2" t="n">
+      <c r="N100" s="1" t="n">
         <v>43201</v>
       </c>
       <c r="O100" t="inlineStr">
@@ -10404,10 +10245,8 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
+      <c r="A101" t="n">
+        <v>1714</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
@@ -10459,7 +10298,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N101" s="2" t="n">
+      <c r="N101" s="1" t="n">
         <v>36871</v>
       </c>
       <c r="O101" t="inlineStr">
@@ -10504,10 +10343,8 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
+      <c r="A102" t="n">
+        <v>1714</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
@@ -10561,7 +10398,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N102" s="2" t="n">
+      <c r="N102" s="1" t="n">
         <v>36561</v>
       </c>
       <c r="O102" t="inlineStr">
@@ -10606,10 +10443,8 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
+      <c r="A103" t="n">
+        <v>1714</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
@@ -10663,7 +10498,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N103" s="2" t="n">
+      <c r="N103" s="1" t="n">
         <v>41058</v>
       </c>
       <c r="O103" t="inlineStr">
@@ -10708,10 +10543,8 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
+      <c r="A104" t="n">
+        <v>1714</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
@@ -10763,7 +10596,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N104" s="2" t="n">
+      <c r="N104" s="1" t="n">
         <v>41309</v>
       </c>
       <c r="O104" t="inlineStr">
@@ -10808,10 +10641,8 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
+      <c r="A105" t="n">
+        <v>1714</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
@@ -10863,7 +10694,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N105" s="2" t="n">
+      <c r="N105" s="1" t="n">
         <v>36859</v>
       </c>
       <c r="O105" t="inlineStr">
@@ -10908,10 +10739,8 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
+      <c r="A106" t="n">
+        <v>1714</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
@@ -10963,7 +10792,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N106" s="2" t="n">
+      <c r="N106" s="1" t="n">
         <v>40127</v>
       </c>
       <c r="O106" t="inlineStr">
@@ -11008,10 +10837,8 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>1714</t>
-        </is>
+      <c r="A107" t="n">
+        <v>1714</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
@@ -11065,7 +10892,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N107" s="2" t="n">
+      <c r="N107" s="1" t="n">
         <v>40435</v>
       </c>
       <c r="O107" t="inlineStr">
@@ -11110,10 +10937,8 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>1716</t>
-        </is>
+      <c r="A108" t="n">
+        <v>1716</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
@@ -11167,7 +10992,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N108" s="2" t="n">
+      <c r="N108" s="1" t="n">
         <v>43003</v>
       </c>
       <c r="O108" t="inlineStr">
@@ -11212,10 +11037,8 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>1722</t>
-        </is>
+      <c r="A109" t="n">
+        <v>1722</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
@@ -11267,7 +11090,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N109" s="2" t="n">
+      <c r="N109" s="1" t="n">
         <v>45649</v>
       </c>
       <c r="O109" t="inlineStr">
@@ -11312,10 +11135,8 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>1726</t>
-        </is>
+      <c r="A110" t="n">
+        <v>1726</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
@@ -11369,7 +11190,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N110" s="2" t="n">
+      <c r="N110" s="1" t="n">
         <v>43077</v>
       </c>
       <c r="O110" t="inlineStr">
@@ -11414,10 +11235,8 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>1728</t>
-        </is>
+      <c r="A111" t="n">
+        <v>1728</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -11469,7 +11288,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N111" s="2" t="n">
+      <c r="N111" s="1" t="n">
         <v>42952</v>
       </c>
       <c r="O111" t="inlineStr">
@@ -11514,10 +11333,8 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>1801</t>
-        </is>
+      <c r="A112" t="n">
+        <v>1801</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -11569,7 +11386,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N112" s="2" t="n">
+      <c r="N112" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O112" t="inlineStr">
@@ -11614,10 +11431,8 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>1801</t>
-        </is>
+      <c r="A113" t="n">
+        <v>1801</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -11669,7 +11484,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N113" s="2" t="n">
+      <c r="N113" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O113" t="inlineStr">
@@ -11714,10 +11529,8 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>1801</t>
-        </is>
+      <c r="A114" t="n">
+        <v>1801</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -11769,7 +11582,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N114" s="2" t="n">
+      <c r="N114" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O114" t="inlineStr">
@@ -11814,10 +11627,8 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>1801</t>
-        </is>
+      <c r="A115" t="n">
+        <v>1801</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -11869,7 +11680,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N115" s="2" t="n">
+      <c r="N115" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O115" t="inlineStr">
@@ -11914,10 +11725,8 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>1801</t>
-        </is>
+      <c r="A116" t="n">
+        <v>1801</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -11969,7 +11778,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N116" s="2" t="n">
+      <c r="N116" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O116" t="inlineStr">
@@ -12014,10 +11823,8 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>1801</t>
-        </is>
+      <c r="A117" t="n">
+        <v>1801</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -12069,7 +11876,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N117" s="2" t="n">
+      <c r="N117" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O117" t="inlineStr">
@@ -12114,10 +11921,8 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>1801</t>
-        </is>
+      <c r="A118" t="n">
+        <v>1801</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -12169,7 +11974,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N118" s="2" t="n">
+      <c r="N118" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O118" t="inlineStr">
@@ -12214,10 +12019,8 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>1803</t>
-        </is>
+      <c r="A119" t="n">
+        <v>1803</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -12269,7 +12072,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N119" s="2" t="n">
+      <c r="N119" s="1" t="n">
         <v>41976</v>
       </c>
       <c r="O119" t="inlineStr">
@@ -12314,10 +12117,8 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>1803</t>
-        </is>
+      <c r="A120" t="n">
+        <v>1803</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -12371,7 +12172,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N120" s="2" t="n">
+      <c r="N120" s="1" t="n">
         <v>45272</v>
       </c>
       <c r="O120" t="inlineStr">
@@ -12416,10 +12217,8 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>1805</t>
-        </is>
+      <c r="A121" t="n">
+        <v>1805</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -12473,7 +12272,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N121" s="2" t="n">
+      <c r="N121" s="1" t="n">
         <v>40176</v>
       </c>
       <c r="O121" t="inlineStr">
@@ -12518,10 +12317,8 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A122" t="n">
+        <v>1812</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -12573,7 +12370,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N122" s="2" t="n">
+      <c r="N122" s="1" t="n">
         <v>44267</v>
       </c>
       <c r="O122" t="inlineStr">
@@ -12618,10 +12415,8 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A123" t="n">
+        <v>1812</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -12673,7 +12468,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N123" s="2" t="n">
+      <c r="N123" s="1" t="n">
         <v>36357</v>
       </c>
       <c r="O123" t="inlineStr">
@@ -12718,10 +12513,8 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A124" t="n">
+        <v>1812</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -12773,7 +12566,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N124" s="2" t="n">
+      <c r="N124" s="1" t="n">
         <v>41781</v>
       </c>
       <c r="O124" t="inlineStr">
@@ -12818,10 +12611,8 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A125" t="n">
+        <v>1812</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -12873,7 +12664,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N125" s="2" t="n">
+      <c r="N125" s="1" t="n">
         <v>43481</v>
       </c>
       <c r="O125" t="inlineStr">
@@ -12918,10 +12709,8 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A126" t="n">
+        <v>1812</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -12973,7 +12762,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N126" s="2" t="n">
+      <c r="N126" s="1" t="n">
         <v>40920</v>
       </c>
       <c r="O126" t="inlineStr">
@@ -13018,10 +12807,8 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A127" t="n">
+        <v>1812</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -13073,7 +12860,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N127" s="2" t="n">
+      <c r="N127" s="1" t="n">
         <v>43523</v>
       </c>
       <c r="O127" t="inlineStr">
@@ -13118,10 +12905,8 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A128" t="n">
+        <v>1812</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -13173,7 +12958,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N128" s="2" t="n">
+      <c r="N128" s="1" t="n">
         <v>43281</v>
       </c>
       <c r="O128" t="inlineStr">
@@ -13218,10 +13003,8 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A129" t="n">
+        <v>1812</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -13273,7 +13056,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N129" s="2" t="n">
+      <c r="N129" s="1" t="n">
         <v>40441</v>
       </c>
       <c r="O129" t="inlineStr">
@@ -13318,10 +13101,8 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A130" t="n">
+        <v>1812</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -13373,7 +13154,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N130" s="2" t="n">
+      <c r="N130" s="1" t="n">
         <v>41212</v>
       </c>
       <c r="O130" t="inlineStr">
@@ -13418,10 +13199,8 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A131" t="n">
+        <v>1812</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -13473,7 +13252,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N131" s="2" t="n">
+      <c r="N131" s="1" t="n">
         <v>40945</v>
       </c>
       <c r="O131" t="inlineStr">
@@ -13518,10 +13297,8 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A132" t="n">
+        <v>1812</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -13573,7 +13350,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N132" s="2" t="n">
+      <c r="N132" s="1" t="n">
         <v>40386</v>
       </c>
       <c r="O132" t="inlineStr">
@@ -13618,10 +13395,8 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A133" t="n">
+        <v>1812</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -13673,7 +13448,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N133" s="2" t="n">
+      <c r="N133" s="1" t="n">
         <v>43798</v>
       </c>
       <c r="O133" t="inlineStr">
@@ -13718,10 +13493,8 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A134" t="n">
+        <v>1812</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
@@ -13773,7 +13546,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N134" s="2" t="n">
+      <c r="N134" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O134" t="inlineStr">
@@ -13818,10 +13591,8 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A135" t="n">
+        <v>1812</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
@@ -13873,7 +13644,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N135" s="2" t="n">
+      <c r="N135" s="1" t="n">
         <v>41542</v>
       </c>
       <c r="O135" t="inlineStr">
@@ -13918,10 +13689,8 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A136" t="n">
+        <v>1812</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
@@ -13973,7 +13742,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N136" s="2" t="n">
+      <c r="N136" s="1" t="n">
         <v>42210</v>
       </c>
       <c r="O136" t="inlineStr">
@@ -14018,10 +13787,8 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A137" t="n">
+        <v>1812</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
@@ -14073,7 +13840,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N137" s="2" t="n">
+      <c r="N137" s="1" t="n">
         <v>43817</v>
       </c>
       <c r="O137" t="inlineStr">
@@ -14118,10 +13885,8 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A138" t="n">
+        <v>1812</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
@@ -14173,7 +13938,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N138" s="2" t="n">
+      <c r="N138" s="1" t="n">
         <v>36839</v>
       </c>
       <c r="O138" t="inlineStr">
@@ -14218,10 +13983,8 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A139" t="n">
+        <v>1812</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
@@ -14273,7 +14036,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N139" s="2" t="n">
+      <c r="N139" s="1" t="n">
         <v>40176</v>
       </c>
       <c r="O139" t="inlineStr">
@@ -14318,10 +14081,8 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A140" t="n">
+        <v>1812</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
@@ -14373,7 +14134,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N140" s="2" t="n">
+      <c r="N140" s="1" t="n">
         <v>41899</v>
       </c>
       <c r="O140" t="inlineStr">
@@ -14418,10 +14179,8 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A141" t="n">
+        <v>1812</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -14473,7 +14232,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N141" s="2" t="n">
+      <c r="N141" s="1" t="n">
         <v>36454</v>
       </c>
       <c r="O141" t="inlineStr">
@@ -14518,10 +14277,8 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A142" t="n">
+        <v>1812</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -14573,7 +14330,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N142" s="2" t="n">
+      <c r="N142" s="1" t="n">
         <v>42094</v>
       </c>
       <c r="O142" t="inlineStr">
@@ -14618,10 +14375,8 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A143" t="n">
+        <v>1812</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -14673,7 +14428,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N143" s="2" t="n">
+      <c r="N143" s="1" t="n">
         <v>37098</v>
       </c>
       <c r="O143" t="inlineStr">
@@ -14718,10 +14473,8 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A144" t="n">
+        <v>1812</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -14773,7 +14526,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N144" s="2" t="n">
+      <c r="N144" s="1" t="n">
         <v>41542</v>
       </c>
       <c r="O144" t="inlineStr">
@@ -14818,10 +14571,8 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A145" t="n">
+        <v>1812</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -14873,7 +14624,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N145" s="2" t="n">
+      <c r="N145" s="1" t="n">
         <v>38684</v>
       </c>
       <c r="O145" t="inlineStr">
@@ -14918,10 +14669,8 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A146" t="n">
+        <v>1812</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
@@ -14973,7 +14722,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N146" s="2" t="n">
+      <c r="N146" s="1" t="n">
         <v>37281</v>
       </c>
       <c r="O146" t="inlineStr">
@@ -15018,10 +14767,8 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A147" t="n">
+        <v>1812</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
@@ -15073,7 +14820,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N147" s="2" t="n">
+      <c r="N147" s="1" t="n">
         <v>42199</v>
       </c>
       <c r="O147" t="inlineStr">
@@ -15118,10 +14865,8 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A148" t="n">
+        <v>1812</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
@@ -15173,7 +14918,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N148" s="2" t="n">
+      <c r="N148" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O148" t="inlineStr">
@@ -15218,10 +14963,8 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A149" t="n">
+        <v>1812</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
@@ -15273,7 +15016,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N149" s="2" t="n">
+      <c r="N149" s="1" t="n">
         <v>39783</v>
       </c>
       <c r="O149" t="inlineStr">
@@ -15318,10 +15061,8 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A150" t="n">
+        <v>1812</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
@@ -15373,7 +15114,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N150" s="2" t="n">
+      <c r="N150" s="1" t="n">
         <v>37426</v>
       </c>
       <c r="O150" t="inlineStr">
@@ -15418,10 +15159,8 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A151" t="n">
+        <v>1812</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
@@ -15473,7 +15212,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N151" s="2" t="n">
+      <c r="N151" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O151" t="inlineStr">
@@ -15518,10 +15257,8 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A152" t="n">
+        <v>1812</v>
       </c>
       <c r="B152" t="inlineStr">
         <is>
@@ -15573,7 +15310,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N152" s="2" t="n">
+      <c r="N152" s="1" t="n">
         <v>41845</v>
       </c>
       <c r="O152" t="inlineStr">
@@ -15618,10 +15355,8 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A153" t="n">
+        <v>1812</v>
       </c>
       <c r="B153" t="inlineStr">
         <is>
@@ -15673,7 +15408,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N153" s="2" t="n">
+      <c r="N153" s="1" t="n">
         <v>43845</v>
       </c>
       <c r="O153" t="inlineStr">
@@ -15718,10 +15453,8 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A154" t="n">
+        <v>1812</v>
       </c>
       <c r="B154" t="inlineStr">
         <is>
@@ -15773,7 +15506,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N154" s="2" t="n">
+      <c r="N154" s="1" t="n">
         <v>36104</v>
       </c>
       <c r="O154" t="inlineStr">
@@ -15818,10 +15551,8 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A155" t="n">
+        <v>1812</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -15873,7 +15604,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N155" s="2" t="n">
+      <c r="N155" s="1" t="n">
         <v>41172</v>
       </c>
       <c r="O155" t="inlineStr">
@@ -15918,10 +15649,8 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A156" t="n">
+        <v>1812</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -15973,7 +15702,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N156" s="2" t="n">
+      <c r="N156" s="1" t="n">
         <v>42598</v>
       </c>
       <c r="O156" t="inlineStr">
@@ -16018,10 +15747,8 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A157" t="n">
+        <v>1812</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -16073,7 +15800,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N157" s="2" t="n">
+      <c r="N157" s="1" t="n">
         <v>43817</v>
       </c>
       <c r="O157" t="inlineStr">
@@ -16118,10 +15845,8 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A158" t="n">
+        <v>1812</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -16173,7 +15898,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N158" s="2" t="n">
+      <c r="N158" s="1" t="n">
         <v>41978</v>
       </c>
       <c r="O158" t="inlineStr">
@@ -16218,10 +15943,8 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A159" t="n">
+        <v>1812</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -16273,7 +15996,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N159" s="2" t="n">
+      <c r="N159" s="1" t="n">
         <v>40305</v>
       </c>
       <c r="O159" t="inlineStr">
@@ -16318,10 +16041,8 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A160" t="n">
+        <v>1812</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -16373,7 +16094,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N160" s="2" t="n">
+      <c r="N160" s="1" t="n">
         <v>43173</v>
       </c>
       <c r="O160" t="inlineStr">
@@ -16418,10 +16139,8 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A161" t="n">
+        <v>1812</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -16473,7 +16192,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N161" s="2" t="n">
+      <c r="N161" s="1" t="n">
         <v>42791</v>
       </c>
       <c r="O161" t="inlineStr">
@@ -16518,10 +16237,8 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A162" t="n">
+        <v>1812</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -16573,7 +16290,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N162" s="2" t="n">
+      <c r="N162" s="1" t="n">
         <v>42679</v>
       </c>
       <c r="O162" t="inlineStr">
@@ -16618,10 +16335,8 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A163" t="n">
+        <v>1812</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -16675,7 +16390,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N163" s="2" t="n">
+      <c r="N163" s="1" t="n">
         <v>41781</v>
       </c>
       <c r="O163" t="inlineStr">
@@ -16720,10 +16435,8 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A164" t="n">
+        <v>1812</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -16775,7 +16488,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N164" s="2" t="n">
+      <c r="N164" s="1" t="n">
         <v>40324</v>
       </c>
       <c r="O164" t="inlineStr">
@@ -16820,10 +16533,8 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A165" t="n">
+        <v>1812</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -16875,7 +16586,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N165" s="2" t="n">
+      <c r="N165" s="1" t="n">
         <v>41722</v>
       </c>
       <c r="O165" t="inlineStr">
@@ -16920,10 +16631,8 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A166" t="n">
+        <v>1812</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -16975,7 +16684,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N166" s="2" t="n">
+      <c r="N166" s="1" t="n">
         <v>44343</v>
       </c>
       <c r="O166" t="inlineStr">
@@ -17020,10 +16729,8 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A167" t="n">
+        <v>1812</v>
       </c>
       <c r="B167" t="inlineStr">
         <is>
@@ -17075,7 +16782,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N167" s="2" t="n">
+      <c r="N167" s="1" t="n">
         <v>40372</v>
       </c>
       <c r="O167" t="inlineStr">
@@ -17120,10 +16827,8 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A168" t="n">
+        <v>1812</v>
       </c>
       <c r="B168" t="inlineStr">
         <is>
@@ -17175,7 +16880,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N168" s="2" t="n">
+      <c r="N168" s="1" t="n">
         <v>41842</v>
       </c>
       <c r="O168" t="inlineStr">
@@ -17220,10 +16925,8 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A169" t="n">
+        <v>1812</v>
       </c>
       <c r="B169" t="inlineStr">
         <is>
@@ -17275,7 +16978,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N169" s="2" t="n">
+      <c r="N169" s="1" t="n">
         <v>44363</v>
       </c>
       <c r="O169" t="inlineStr">
@@ -17320,10 +17023,8 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A170" t="n">
+        <v>1812</v>
       </c>
       <c r="B170" t="inlineStr">
         <is>
@@ -17375,7 +17076,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N170" s="2" t="n">
+      <c r="N170" s="1" t="n">
         <v>40648</v>
       </c>
       <c r="O170" t="inlineStr">
@@ -17420,10 +17121,8 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A171" t="n">
+        <v>1812</v>
       </c>
       <c r="B171" t="inlineStr">
         <is>
@@ -17475,7 +17174,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N171" s="2" t="n">
+      <c r="N171" s="1" t="n">
         <v>43816</v>
       </c>
       <c r="O171" t="inlineStr">
@@ -17520,10 +17219,8 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A172" t="n">
+        <v>1812</v>
       </c>
       <c r="B172" t="inlineStr">
         <is>
@@ -17575,7 +17272,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N172" s="2" t="n">
+      <c r="N172" s="1" t="n">
         <v>41421</v>
       </c>
       <c r="O172" t="inlineStr">
@@ -17620,10 +17317,8 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A173" t="n">
+        <v>1812</v>
       </c>
       <c r="B173" t="inlineStr">
         <is>
@@ -17675,7 +17370,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N173" s="2" t="n">
+      <c r="N173" s="1" t="n">
         <v>43529</v>
       </c>
       <c r="O173" t="inlineStr">
@@ -17720,10 +17415,8 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A174" t="n">
+        <v>1812</v>
       </c>
       <c r="B174" t="inlineStr">
         <is>
@@ -17775,7 +17468,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N174" s="2" t="n">
+      <c r="N174" s="1" t="n">
         <v>42080</v>
       </c>
       <c r="O174" t="inlineStr">
@@ -17820,10 +17513,8 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A175" t="n">
+        <v>1812</v>
       </c>
       <c r="B175" t="inlineStr">
         <is>
@@ -17875,7 +17566,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N175" s="2" t="n">
+      <c r="N175" s="1" t="n">
         <v>43826</v>
       </c>
       <c r="O175" t="inlineStr">
@@ -17920,10 +17611,8 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A176" t="n">
+        <v>1812</v>
       </c>
       <c r="B176" t="inlineStr">
         <is>
@@ -17975,7 +17664,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N176" s="2" t="n">
+      <c r="N176" s="1" t="n">
         <v>42581</v>
       </c>
       <c r="O176" t="inlineStr">
@@ -18020,10 +17709,8 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A177" t="n">
+        <v>1812</v>
       </c>
       <c r="B177" t="inlineStr">
         <is>
@@ -18075,7 +17762,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N177" s="2" t="n">
+      <c r="N177" s="1" t="n">
         <v>41869</v>
       </c>
       <c r="O177" t="inlineStr">
@@ -18120,10 +17807,8 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A178" t="n">
+        <v>1812</v>
       </c>
       <c r="B178" t="inlineStr">
         <is>
@@ -18175,7 +17860,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N178" s="2" t="n">
+      <c r="N178" s="1" t="n">
         <v>44530</v>
       </c>
       <c r="O178" t="inlineStr">
@@ -18220,10 +17905,8 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A179" t="n">
+        <v>1812</v>
       </c>
       <c r="B179" t="inlineStr">
         <is>
@@ -18275,7 +17958,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N179" s="2" t="n">
+      <c r="N179" s="1" t="n">
         <v>43458</v>
       </c>
       <c r="O179" t="inlineStr">
@@ -18320,10 +18003,8 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A180" t="n">
+        <v>1812</v>
       </c>
       <c r="B180" t="inlineStr">
         <is>
@@ -18375,7 +18056,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N180" s="2" t="n">
+      <c r="N180" s="1" t="n">
         <v>40942</v>
       </c>
       <c r="O180" t="inlineStr">
@@ -18420,10 +18101,8 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A181" t="n">
+        <v>1812</v>
       </c>
       <c r="B181" t="inlineStr">
         <is>
@@ -18475,7 +18154,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N181" s="2" t="n">
+      <c r="N181" s="1" t="n">
         <v>41464</v>
       </c>
       <c r="O181" t="inlineStr">
@@ -18520,10 +18199,8 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A182" t="n">
+        <v>1812</v>
       </c>
       <c r="B182" t="inlineStr">
         <is>
@@ -18575,7 +18252,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N182" s="2" t="n">
+      <c r="N182" s="1" t="n">
         <v>41464</v>
       </c>
       <c r="O182" t="inlineStr">
@@ -18620,10 +18297,8 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A183" t="n">
+        <v>1812</v>
       </c>
       <c r="B183" t="inlineStr">
         <is>
@@ -18675,7 +18350,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N183" s="2" t="n">
+      <c r="N183" s="1" t="n">
         <v>41630</v>
       </c>
       <c r="O183" t="inlineStr">
@@ -18720,10 +18395,8 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A184" t="n">
+        <v>1812</v>
       </c>
       <c r="B184" t="inlineStr">
         <is>
@@ -18775,7 +18448,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N184" s="2" t="n">
+      <c r="N184" s="1" t="n">
         <v>41464</v>
       </c>
       <c r="O184" t="inlineStr">
@@ -18820,10 +18493,8 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>1812</t>
-        </is>
+      <c r="A185" t="n">
+        <v>1812</v>
       </c>
       <c r="B185" t="inlineStr">
         <is>
@@ -18875,7 +18546,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N185" s="2" t="n">
+      <c r="N185" s="1" t="n">
         <v>41172</v>
       </c>
       <c r="O185" t="inlineStr">
@@ -18920,10 +18591,8 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>1813</t>
-        </is>
+      <c r="A186" t="n">
+        <v>1813</v>
       </c>
       <c r="B186" t="inlineStr">
         <is>
@@ -18977,7 +18646,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N186" s="2" t="n">
+      <c r="N186" s="1" t="n">
         <v>40176</v>
       </c>
       <c r="O186" t="inlineStr">
@@ -19022,10 +18691,8 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>1813</t>
-        </is>
+      <c r="A187" t="n">
+        <v>1813</v>
       </c>
       <c r="B187" t="inlineStr">
         <is>
@@ -19077,7 +18744,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N187" s="2" t="n">
+      <c r="N187" s="1" t="n">
         <v>40108</v>
       </c>
       <c r="O187" t="inlineStr">
@@ -19122,10 +18789,8 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>1823</t>
-        </is>
+      <c r="A188" t="n">
+        <v>1823</v>
       </c>
       <c r="B188" t="inlineStr">
         <is>
@@ -19177,7 +18842,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N188" s="2" t="n">
+      <c r="N188" s="1" t="n">
         <v>43495</v>
       </c>
       <c r="O188" t="inlineStr">
@@ -19222,10 +18887,8 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>1823</t>
-        </is>
+      <c r="A189" t="n">
+        <v>1823</v>
       </c>
       <c r="B189" t="inlineStr">
         <is>
@@ -19277,7 +18940,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N189" s="2" t="n">
+      <c r="N189" s="1" t="n">
         <v>43327</v>
       </c>
       <c r="O189" t="inlineStr">
@@ -19322,10 +18985,8 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>1824</t>
-        </is>
+      <c r="A190" t="n">
+        <v>1824</v>
       </c>
       <c r="B190" t="inlineStr">
         <is>
@@ -19377,7 +19038,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N190" s="2" t="n">
+      <c r="N190" s="1" t="n">
         <v>41283</v>
       </c>
       <c r="O190" t="inlineStr">
@@ -19422,10 +19083,8 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>1826</t>
-        </is>
+      <c r="A191" t="n">
+        <v>1826</v>
       </c>
       <c r="B191" t="inlineStr">
         <is>
@@ -19479,7 +19138,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N191" s="2" t="n">
+      <c r="N191" s="1" t="n">
         <v>42137</v>
       </c>
       <c r="O191" t="inlineStr">
@@ -19524,10 +19183,8 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
+      <c r="A192" t="n">
+        <v>1828</v>
       </c>
       <c r="B192" t="inlineStr">
         <is>
@@ -19579,7 +19236,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N192" s="2" t="n">
+      <c r="N192" s="1" t="n">
         <v>41799</v>
       </c>
       <c r="O192" t="inlineStr">
@@ -19624,10 +19281,8 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr">
-        <is>
-          <t>1828</t>
-        </is>
+      <c r="A193" t="n">
+        <v>1828</v>
       </c>
       <c r="B193" t="inlineStr">
         <is>
@@ -19679,7 +19334,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N193" s="2" t="n">
+      <c r="N193" s="1" t="n">
         <v>41822</v>
       </c>
       <c r="O193" t="inlineStr">
@@ -19724,10 +19379,8 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>1832</t>
-        </is>
+      <c r="A194" t="n">
+        <v>1832</v>
       </c>
       <c r="B194" t="inlineStr">
         <is>
@@ -19779,7 +19432,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N194" s="2" t="n">
+      <c r="N194" s="1" t="n">
         <v>42858</v>
       </c>
       <c r="O194" t="inlineStr">
@@ -19824,10 +19477,8 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr">
-        <is>
-          <t>1833</t>
-        </is>
+      <c r="A195" t="n">
+        <v>1833</v>
       </c>
       <c r="B195" t="inlineStr">
         <is>
@@ -19879,7 +19530,7 @@
           <t>Sin definir</t>
         </is>
       </c>
-      <c r="N195" s="2" t="n">
+      <c r="N195" s="1" t="n">
         <v>37055</v>
       </c>
       <c r="O195" t="inlineStr">
@@ -19924,10 +19575,8 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr">
-        <is>
-          <t>1833</t>
-        </is>
+      <c r="A196" t="n">
+        <v>1833</v>
       </c>
       <c r="B196" t="inlineStr">
         <is>
@@ -19979,7 +19628,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N196" s="2" t="n">
+      <c r="N196" s="1" t="n">
         <v>39640</v>
       </c>
       <c r="O196" t="inlineStr">
@@ -20024,10 +19673,8 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="inlineStr">
-        <is>
-          <t>1833</t>
-        </is>
+      <c r="A197" t="n">
+        <v>1833</v>
       </c>
       <c r="B197" t="inlineStr">
         <is>
@@ -20079,7 +19726,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N197" s="2" t="n">
+      <c r="N197" s="1" t="n">
         <v>39329</v>
       </c>
       <c r="O197" t="inlineStr">
@@ -20124,10 +19771,8 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr">
-        <is>
-          <t>1833</t>
-        </is>
+      <c r="A198" t="n">
+        <v>1833</v>
       </c>
       <c r="B198" t="inlineStr">
         <is>
@@ -20179,7 +19824,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N198" s="2" t="n">
+      <c r="N198" s="1" t="n">
         <v>40723</v>
       </c>
       <c r="O198" t="inlineStr">
@@ -20224,10 +19869,8 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="inlineStr">
-        <is>
-          <t>2106</t>
-        </is>
+      <c r="A199" t="n">
+        <v>2106</v>
       </c>
       <c r="B199" t="inlineStr">
         <is>
@@ -20281,7 +19924,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N199" s="2" t="n">
+      <c r="N199" s="1" t="n">
         <v>38944</v>
       </c>
       <c r="O199" t="inlineStr">
@@ -20326,10 +19969,8 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>2106</t>
-        </is>
+      <c r="A200" t="n">
+        <v>2106</v>
       </c>
       <c r="B200" t="inlineStr">
         <is>
@@ -20383,7 +20024,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N200" s="2" t="n">
+      <c r="N200" s="1" t="n">
         <v>39437</v>
       </c>
       <c r="O200" t="inlineStr">
@@ -20428,10 +20069,8 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>2209</t>
-        </is>
+      <c r="A201" t="n">
+        <v>2209</v>
       </c>
       <c r="B201" t="inlineStr">
         <is>
@@ -20483,7 +20122,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N201" s="2" t="n">
+      <c r="N201" s="1" t="n">
         <v>41758</v>
       </c>
       <c r="O201" t="inlineStr">
@@ -20528,10 +20167,8 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>2209</t>
-        </is>
+      <c r="A202" t="n">
+        <v>2209</v>
       </c>
       <c r="B202" t="inlineStr">
         <is>
@@ -20585,7 +20222,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N202" s="2" t="n">
+      <c r="N202" s="1" t="n">
         <v>43172</v>
       </c>
       <c r="O202" t="inlineStr">
@@ -20630,10 +20267,8 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>2209</t>
-        </is>
+      <c r="A203" t="n">
+        <v>2209</v>
       </c>
       <c r="B203" t="inlineStr">
         <is>
@@ -20685,7 +20320,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N203" s="2" t="n">
+      <c r="N203" s="1" t="n">
         <v>41974</v>
       </c>
       <c r="O203" t="inlineStr">
@@ -20730,10 +20365,8 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>2702</t>
-        </is>
+      <c r="A204" t="n">
+        <v>2702</v>
       </c>
       <c r="B204" t="inlineStr">
         <is>
@@ -20785,7 +20418,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N204" s="2" t="n">
+      <c r="N204" s="1" t="n">
         <v>36914</v>
       </c>
       <c r="O204" t="inlineStr">
@@ -20830,10 +20463,8 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>2707</t>
-        </is>
+      <c r="A205" t="n">
+        <v>2707</v>
       </c>
       <c r="B205" t="inlineStr">
         <is>
@@ -20885,7 +20516,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N205" s="2" t="n">
+      <c r="N205" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O205" t="inlineStr">
@@ -20930,10 +20561,8 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>2707</t>
-        </is>
+      <c r="A206" t="n">
+        <v>2707</v>
       </c>
       <c r="B206" t="inlineStr">
         <is>
@@ -20985,7 +20614,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N206" s="2" t="n">
+      <c r="N206" s="1" t="n">
         <v>41202</v>
       </c>
       <c r="O206" t="inlineStr">
@@ -21030,10 +20659,8 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>2707</t>
-        </is>
+      <c r="A207" t="n">
+        <v>2707</v>
       </c>
       <c r="B207" t="inlineStr">
         <is>
@@ -21085,7 +20712,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N207" s="2" t="n">
+      <c r="N207" s="1" t="n">
         <v>42404</v>
       </c>
       <c r="O207" t="inlineStr">
@@ -21130,10 +20757,8 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>2711</t>
-        </is>
+      <c r="A208" t="n">
+        <v>2711</v>
       </c>
       <c r="B208" t="inlineStr">
         <is>
@@ -21187,7 +20812,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N208" s="2" t="n">
+      <c r="N208" s="1" t="n">
         <v>44323</v>
       </c>
       <c r="O208" t="inlineStr">
@@ -21232,10 +20857,8 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>2712</t>
-        </is>
+      <c r="A209" t="n">
+        <v>2712</v>
       </c>
       <c r="B209" t="inlineStr">
         <is>
@@ -21289,7 +20912,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N209" s="2" t="n">
+      <c r="N209" s="1" t="n">
         <v>43662</v>
       </c>
       <c r="O209" t="inlineStr">
@@ -21334,10 +20957,8 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>2713</t>
-        </is>
+      <c r="A210" t="n">
+        <v>2713</v>
       </c>
       <c r="B210" t="inlineStr">
         <is>
@@ -21391,7 +21012,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N210" s="2" t="n">
+      <c r="N210" s="1" t="n">
         <v>42978</v>
       </c>
       <c r="O210" t="inlineStr">
@@ -21436,10 +21057,8 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>2725</t>
-        </is>
+      <c r="A211" t="n">
+        <v>2725</v>
       </c>
       <c r="B211" t="inlineStr">
         <is>
@@ -21493,7 +21112,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N211" s="2" t="n">
+      <c r="N211" s="1" t="n">
         <v>43315</v>
       </c>
       <c r="O211" t="inlineStr">
@@ -21538,10 +21157,8 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>2727</t>
-        </is>
+      <c r="A212" t="n">
+        <v>2727</v>
       </c>
       <c r="B212" t="inlineStr">
         <is>
@@ -21593,7 +21210,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N212" s="2" t="n">
+      <c r="N212" s="1" t="n">
         <v>42811</v>
       </c>
       <c r="O212" t="inlineStr">
@@ -21638,10 +21255,8 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>2727</t>
-        </is>
+      <c r="A213" t="n">
+        <v>2727</v>
       </c>
       <c r="B213" t="inlineStr">
         <is>
@@ -21693,7 +21308,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N213" s="2" t="n">
+      <c r="N213" s="1" t="n">
         <v>41672</v>
       </c>
       <c r="O213" t="inlineStr">
@@ -21738,10 +21353,8 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>2810</t>
-        </is>
+      <c r="A214" t="n">
+        <v>2810</v>
       </c>
       <c r="B214" t="inlineStr">
         <is>
@@ -21795,7 +21408,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N214" s="2" t="n">
+      <c r="N214" s="1" t="n">
         <v>45211</v>
       </c>
       <c r="O214" t="inlineStr">
@@ -21840,10 +21453,8 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>2810</t>
-        </is>
+      <c r="A215" t="n">
+        <v>2810</v>
       </c>
       <c r="B215" t="inlineStr">
         <is>
@@ -21895,7 +21506,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N215" s="2" t="n">
+      <c r="N215" s="1" t="n">
         <v>45211</v>
       </c>
       <c r="O215" t="inlineStr">
@@ -21940,10 +21551,8 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>2810</t>
-        </is>
+      <c r="A216" t="n">
+        <v>2810</v>
       </c>
       <c r="B216" t="inlineStr">
         <is>
@@ -21997,7 +21606,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N216" s="2" t="n">
+      <c r="N216" s="1" t="n">
         <v>45352</v>
       </c>
       <c r="O216" t="inlineStr">
@@ -22042,10 +21651,8 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>2813</t>
-        </is>
+      <c r="A217" t="n">
+        <v>2813</v>
       </c>
       <c r="B217" t="inlineStr">
         <is>
@@ -22099,7 +21706,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N217" s="2" t="n">
+      <c r="N217" s="1" t="n">
         <v>43283</v>
       </c>
       <c r="O217" t="inlineStr">
@@ -22144,10 +21751,8 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>2832</t>
-        </is>
+      <c r="A218" t="n">
+        <v>2832</v>
       </c>
       <c r="B218" t="inlineStr">
         <is>
@@ -22201,7 +21806,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N218" s="2" t="n">
+      <c r="N218" s="1" t="n">
         <v>42791</v>
       </c>
       <c r="O218" t="inlineStr">
@@ -22246,10 +21851,8 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>2850</t>
-        </is>
+      <c r="A219" t="n">
+        <v>2850</v>
       </c>
       <c r="B219" t="inlineStr">
         <is>
@@ -22301,7 +21904,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N219" s="2" t="n">
+      <c r="N219" s="1" t="n">
         <v>42105</v>
       </c>
       <c r="O219" t="inlineStr">
@@ -22346,10 +21949,8 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>3204</t>
-        </is>
+      <c r="A220" t="n">
+        <v>3204</v>
       </c>
       <c r="B220" t="inlineStr">
         <is>
@@ -22401,7 +22002,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N220" s="2" t="n">
+      <c r="N220" s="1" t="n">
         <v>42875</v>
       </c>
       <c r="O220" t="inlineStr">
@@ -22446,10 +22047,8 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>4108</t>
-        </is>
+      <c r="A221" t="n">
+        <v>4108</v>
       </c>
       <c r="B221" t="inlineStr">
         <is>
@@ -22503,7 +22102,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N221" s="2" t="n">
+      <c r="N221" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O221" t="inlineStr">
@@ -22548,10 +22147,8 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>4108</t>
-        </is>
+      <c r="A222" t="n">
+        <v>4108</v>
       </c>
       <c r="B222" t="inlineStr">
         <is>
@@ -22605,7 +22202,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N222" s="2" t="n">
+      <c r="N222" s="1" t="n">
         <v>35875</v>
       </c>
       <c r="O222" t="inlineStr">
@@ -22650,10 +22247,8 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>4108</t>
-        </is>
+      <c r="A223" t="n">
+        <v>4108</v>
       </c>
       <c r="B223" t="inlineStr">
         <is>
@@ -22707,7 +22302,7 @@
           <t>Trimestral</t>
         </is>
       </c>
-      <c r="N223" s="2" t="n">
+      <c r="N223" s="1" t="n">
         <v>38972</v>
       </c>
       <c r="O223" t="inlineStr">
@@ -22752,10 +22347,8 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>9116</t>
-        </is>
+      <c r="A224" t="n">
+        <v>9116</v>
       </c>
       <c r="B224" t="inlineStr">
         <is>
@@ -22809,7 +22402,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N224" s="2" t="n">
+      <c r="N224" s="1" t="n">
         <v>43363</v>
       </c>
       <c r="O224" t="inlineStr">
@@ -22854,10 +22447,8 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>9116</t>
-        </is>
+      <c r="A225" t="n">
+        <v>9116</v>
       </c>
       <c r="B225" t="inlineStr">
         <is>
@@ -22909,7 +22500,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N225" s="2" t="n">
+      <c r="N225" s="1" t="n">
         <v>47452</v>
       </c>
       <c r="O225" t="inlineStr">
@@ -22954,10 +22545,8 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>9116</t>
-        </is>
+      <c r="A226" t="n">
+        <v>9116</v>
       </c>
       <c r="B226" t="inlineStr">
         <is>
@@ -23009,7 +22598,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N226" s="2" t="n">
+      <c r="N226" s="1" t="n">
         <v>43315</v>
       </c>
       <c r="O226" t="inlineStr">
@@ -23054,10 +22643,8 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>9930</t>
-        </is>
+      <c r="A227" t="n">
+        <v>9930</v>
       </c>
       <c r="B227" t="inlineStr">
         <is>
@@ -23111,7 +22698,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N227" s="2" t="n">
+      <c r="N227" s="1" t="n">
         <v>44096</v>
       </c>
       <c r="O227" t="inlineStr">
@@ -23156,10 +22743,8 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>9930</t>
-        </is>
+      <c r="A228" t="n">
+        <v>9930</v>
       </c>
       <c r="B228" t="inlineStr">
         <is>
@@ -23213,7 +22798,7 @@
           <t>Por cohorte</t>
         </is>
       </c>
-      <c r="N228" s="2" t="n">
+      <c r="N228" s="1" t="n">
         <v>44092</v>
       </c>
       <c r="O228" t="inlineStr">

--- a/data/novedades/Inactivos_posgrado.xlsx
+++ b/data/novedades/Inactivos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V266"/>
+  <dimension ref="A1:V268"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25822,10 +25822,8 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>1713</t>
-        </is>
+      <c r="A259" t="n">
+        <v>1713</v>
       </c>
       <c r="B259" t="inlineStr">
         <is>
@@ -25879,7 +25877,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N259" s="2" t="n">
+      <c r="N259" s="1" t="n">
         <v>44419</v>
       </c>
       <c r="O259" t="inlineStr">
@@ -25924,10 +25922,8 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>1713</t>
-        </is>
+      <c r="A260" t="n">
+        <v>1713</v>
       </c>
       <c r="B260" t="inlineStr">
         <is>
@@ -25979,7 +25975,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N260" s="2" t="n">
+      <c r="N260" s="1" t="n">
         <v>43542</v>
       </c>
       <c r="O260" t="inlineStr">
@@ -26024,10 +26020,8 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>1727</t>
-        </is>
+      <c r="A261" t="n">
+        <v>1727</v>
       </c>
       <c r="B261" t="inlineStr">
         <is>
@@ -26081,7 +26075,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N261" s="2" t="n">
+      <c r="N261" s="1" t="n">
         <v>43277</v>
       </c>
       <c r="O261" t="inlineStr">
@@ -26126,10 +26120,8 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>1823</t>
-        </is>
+      <c r="A262" t="n">
+        <v>1823</v>
       </c>
       <c r="B262" t="inlineStr">
         <is>
@@ -26181,7 +26173,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N262" s="2" t="n">
+      <c r="N262" s="1" t="n">
         <v>43755</v>
       </c>
       <c r="O262" t="inlineStr">
@@ -26226,10 +26218,8 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>1830</t>
-        </is>
+      <c r="A263" t="n">
+        <v>1830</v>
       </c>
       <c r="B263" t="inlineStr">
         <is>
@@ -26283,7 +26273,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N263" s="2" t="n">
+      <c r="N263" s="1" t="n">
         <v>40429</v>
       </c>
       <c r="O263" t="inlineStr">
@@ -26328,10 +26318,8 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="A264" t="n">
+        <v>2102</v>
       </c>
       <c r="B264" t="inlineStr">
         <is>
@@ -26385,7 +26373,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N264" s="2" t="n">
+      <c r="N264" s="1" t="n">
         <v>45114</v>
       </c>
       <c r="O264" t="inlineStr">
@@ -26430,10 +26418,8 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>2102</t>
-        </is>
+      <c r="A265" t="n">
+        <v>2102</v>
       </c>
       <c r="B265" t="inlineStr">
         <is>
@@ -26487,7 +26473,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N265" s="2" t="n">
+      <c r="N265" s="1" t="n">
         <v>42242</v>
       </c>
       <c r="O265" t="inlineStr">
@@ -26532,10 +26518,8 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>2805</t>
-        </is>
+      <c r="A266" t="n">
+        <v>2805</v>
       </c>
       <c r="B266" t="inlineStr">
         <is>
@@ -26589,7 +26573,7 @@
           <t>Semestral</t>
         </is>
       </c>
-      <c r="N266" s="2" t="n">
+      <c r="N266" s="1" t="n">
         <v>43817</v>
       </c>
       <c r="O266" t="inlineStr">
@@ -26630,6 +26614,210 @@
       <c r="V266" t="inlineStr">
         <is>
           <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>1701</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>PONTIFICIA UNIVERSIDAD JAVERIANA</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F267" t="n">
+        <v>108258</v>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN DERECHO DE LA COMPETENCIA</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I267" t="n">
+        <v>29</v>
+      </c>
+      <c r="J267" t="n">
+        <v>2</v>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L267" t="n">
+        <v>14195653</v>
+      </c>
+      <c r="M267" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N267" s="2" t="n">
+        <v>43691</v>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q267" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R267" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T267" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V267" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>1713</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL NORTE</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>Barranquilla</t>
+        </is>
+      </c>
+      <c r="F268" t="n">
+        <v>90970</v>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>DOCTORADO EN COMUNICACIÓN</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I268" t="n">
+        <v>80</v>
+      </c>
+      <c r="J268" t="n">
+        <v>8</v>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L268" t="n">
+        <v>21319356</v>
+      </c>
+      <c r="M268" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N268" s="2" t="n">
+        <v>46038</v>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>Periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>Periodismo, comunicación y reportajes</t>
+        </is>
+      </c>
+      <c r="R268" t="inlineStr">
+        <is>
+          <t>Comunicación social, periodismo y afines</t>
+        </is>
+      </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="T268" t="inlineStr">
+        <is>
+          <t>06/07/2026</t>
+        </is>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V268" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
         </is>
       </c>
     </row>

--- a/data/novedades/Inactivos_posgrado.xlsx
+++ b/data/novedades/Inactivos_posgrado.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V268"/>
+  <dimension ref="A1:V280"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26618,10 +26618,8 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" t="inlineStr">
-        <is>
-          <t>1701</t>
-        </is>
+      <c r="A267" t="n">
+        <v>1701</v>
       </c>
       <c r="B267" t="inlineStr">
         <is>
@@ -26675,7 +26673,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N267" s="2" t="n">
+      <c r="N267" s="1" t="n">
         <v>43691</v>
       </c>
       <c r="O267" t="inlineStr">
@@ -26720,10 +26718,8 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" t="inlineStr">
-        <is>
-          <t>1713</t>
-        </is>
+      <c r="A268" t="n">
+        <v>1713</v>
       </c>
       <c r="B268" t="inlineStr">
         <is>
@@ -26777,7 +26773,7 @@
           <t>Anual</t>
         </is>
       </c>
-      <c r="N268" s="2" t="n">
+      <c r="N268" s="1" t="n">
         <v>46038</v>
       </c>
       <c r="O268" t="inlineStr">
@@ -26818,6 +26814,1220 @@
       <c r="V268" t="inlineStr">
         <is>
           <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>1119</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE LOS LLANOS</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>Villavicencio</t>
+        </is>
+      </c>
+      <c r="F269" t="n">
+        <v>102134</v>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN ACCION MOTRIZ</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I269" t="n">
+        <v>30</v>
+      </c>
+      <c r="J269" t="n">
+        <v>2</v>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr"/>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>Por cohorte</t>
+        </is>
+      </c>
+      <c r="N269" s="2" t="n">
+        <v>41271</v>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a salud y bienestar</t>
+        </is>
+      </c>
+      <c r="Q269" t="inlineStr">
+        <is>
+          <t>Programas y certificaciones interdisciplinarios relativos a salud y bienestar</t>
+        </is>
+      </c>
+      <c r="R269" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T269" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V269" t="inlineStr">
+        <is>
+          <t>Otro</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>1203</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL VALLE</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Oficial</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F270" t="n">
+        <v>107748</v>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>DOCTORADO EN INGENIERIA MECANICA</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I270" t="n">
+        <v>100</v>
+      </c>
+      <c r="J270" t="n">
+        <v>4</v>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L270" t="n">
+        <v>8012643</v>
+      </c>
+      <c r="M270" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N270" s="2" t="n">
+        <v>43558</v>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>Ingeniería, Industria y Construcción</t>
+        </is>
+      </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines</t>
+        </is>
+      </c>
+      <c r="Q270" t="inlineStr">
+        <is>
+          <t>Ingeniería y profesiones afines no clasificadas en otra parte</t>
+        </is>
+      </c>
+      <c r="R270" t="inlineStr">
+        <is>
+          <t>Ingeniería mecánica y afines</t>
+        </is>
+      </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>Doctorado</t>
+        </is>
+      </c>
+      <c r="T270" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V270" t="inlineStr">
+        <is>
+          <t>Ingenierías</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>1704</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTO TOMAS</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F271" t="n">
+        <v>106897</v>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>MAESTRÍA EN CALIDAD Y GESTIÓN INTEGRAL</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I271" t="n">
+        <v>48</v>
+      </c>
+      <c r="J271" t="n">
+        <v>4</v>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L271" t="n">
+        <v>10798104</v>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N271" s="2" t="n">
+        <v>43244</v>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q271" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R271" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S271" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T271" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V271" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>1705</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTO TOMAS</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>Bucaramanga</t>
+        </is>
+      </c>
+      <c r="F272" t="n">
+        <v>101715</v>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN DERECHO DE LAS RELACIONES LABORALES</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I272" t="n">
+        <v>27</v>
+      </c>
+      <c r="J272" t="n">
+        <v>2</v>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L272" t="n">
+        <v>6961500</v>
+      </c>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N272" s="2" t="n">
+        <v>43746</v>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>Derecho</t>
+        </is>
+      </c>
+      <c r="R272" t="inlineStr">
+        <is>
+          <t>Derecho y afines</t>
+        </is>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T272" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V272" t="inlineStr">
+        <is>
+          <t>Derecho, C. Política y Rel. Internacionales</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>1713</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DEL NORTE</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>Riohacha</t>
+        </is>
+      </c>
+      <c r="F273" t="n">
+        <v>103009</v>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN GERENCIA DE LA CALIDAD Y AUDITORÍA EN SALUD</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I273" t="n">
+        <v>30</v>
+      </c>
+      <c r="J273" t="n">
+        <v>2</v>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr"/>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="N273" s="2" t="n">
+        <v>44204</v>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q273" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R273" t="inlineStr">
+        <is>
+          <t>Administración</t>
+        </is>
+      </c>
+      <c r="S273" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T273" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>1722</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE MANIZALES</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>Quindío</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>Armenia</t>
+        </is>
+      </c>
+      <c r="F274" t="n">
+        <v>109667</v>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>MAESTRIA EN TRIBUTACIÓN</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I274" t="n">
+        <v>50</v>
+      </c>
+      <c r="J274" t="n">
+        <v>4</v>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Periodos</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr"/>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N274" s="2" t="n">
+        <v>44153</v>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q274" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R274" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S274" t="inlineStr">
+        <is>
+          <t>Maestría</t>
+        </is>
+      </c>
+      <c r="T274" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V274" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>1732</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD SANTO TOMAS</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>Tunja</t>
+        </is>
+      </c>
+      <c r="F275" t="n">
+        <v>108827</v>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN AUDITORÍA Y ASEGURAMIENTO DE LA INFORMACIÓN</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I275" t="n">
+        <v>24</v>
+      </c>
+      <c r="J275" t="n">
+        <v>2</v>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L275" t="n">
+        <v>5900000</v>
+      </c>
+      <c r="M275" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N275" s="2" t="n">
+        <v>43817</v>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q275" t="inlineStr">
+        <is>
+          <t>Contabilidad e impuestos</t>
+        </is>
+      </c>
+      <c r="R275" t="inlineStr">
+        <is>
+          <t>Contaduría pública</t>
+        </is>
+      </c>
+      <c r="S275" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T275" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V275" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>1830</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DE OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>Ibagué</t>
+        </is>
+      </c>
+      <c r="F276" t="n">
+        <v>110784</v>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN COMUNICACION ORGANIZACIONAL</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I276" t="n">
+        <v>25</v>
+      </c>
+      <c r="J276" t="n">
+        <v>2</v>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr"/>
+      <c r="M276" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N276" s="2" t="n">
+        <v>44258</v>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>Periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q276" t="inlineStr">
+        <is>
+          <t>Periodismo, comunicación y reportajes</t>
+        </is>
+      </c>
+      <c r="R276" t="inlineStr">
+        <is>
+          <t>Comunicación social, periodismo y afines</t>
+        </is>
+      </c>
+      <c r="S276" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V276" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>1830</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD AUTONOMA DE OCCIDENTE</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Valle del Cauca</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>Santiago de Cali</t>
+        </is>
+      </c>
+      <c r="F277" t="n">
+        <v>20110</v>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN COMUNICACION ORGANIZACIONAL</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I277" t="n">
+        <v>25</v>
+      </c>
+      <c r="J277" t="n">
+        <v>2</v>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L277" t="n">
+        <v>9779900</v>
+      </c>
+      <c r="M277" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N277" s="2" t="n">
+        <v>44273</v>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>Ciencias Sociales, Periodismo e Información</t>
+        </is>
+      </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>Periodismo e información</t>
+        </is>
+      </c>
+      <c r="Q277" t="inlineStr">
+        <is>
+          <t>Periodismo, comunicación y reportajes</t>
+        </is>
+      </c>
+      <c r="R277" t="inlineStr">
+        <is>
+          <t>Comunicación social, periodismo y afines</t>
+        </is>
+      </c>
+      <c r="S277" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T277" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V277" t="inlineStr">
+        <is>
+          <t>Humanidades y Cs. Sociales</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>2732</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA CATOLICA DEL NORTE</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>Santa Rosa de Osos</t>
+        </is>
+      </c>
+      <c r="F278" t="n">
+        <v>107864</v>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACION EN GESTIÓN GERONTOLÓGICA</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>Virtual</t>
+        </is>
+      </c>
+      <c r="I278" t="n">
+        <v>26</v>
+      </c>
+      <c r="J278" t="n">
+        <v>2</v>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L278" t="n">
+        <v>5331500</v>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N278" s="2" t="n">
+        <v>43500</v>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>Administración de Empresas y Derecho</t>
+        </is>
+      </c>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>Educación comercial y administración</t>
+        </is>
+      </c>
+      <c r="Q278" t="inlineStr">
+        <is>
+          <t>Gestión y administración</t>
+        </is>
+      </c>
+      <c r="R278" t="inlineStr">
+        <is>
+          <t>Salud pública</t>
+        </is>
+      </c>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T278" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V278" t="inlineStr">
+        <is>
+          <t>Escuela de Negocios</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>2747</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>INSTITUCIÓN UNIVERSITARIA VISIÓN DE LAS AMÉRICAS</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="F279" t="n">
+        <v>107148</v>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN REHABILITACIÓN CARDIOPULMONAR</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I279" t="n">
+        <v>36</v>
+      </c>
+      <c r="J279" t="n">
+        <v>3</v>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="L279" t="n">
+        <v>11002624</v>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="N279" s="2" t="n">
+        <v>43290</v>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>Salud y Bienestar</t>
+        </is>
+      </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>Fisioterapia, Fonoaudiología, Terapia ocupacional, Nutrición y afines</t>
+        </is>
+      </c>
+      <c r="R279" t="inlineStr">
+        <is>
+          <t>Terapias</t>
+        </is>
+      </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T279" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V279" t="inlineStr">
+        <is>
+          <t>Ciencias de la Salud</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>9129</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>FUNDACION UNIVERSITARIA CAFAM -UNICAFAM</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Privado</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>Bogotá, D.C.</t>
+        </is>
+      </c>
+      <c r="F280" t="n">
+        <v>105338</v>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>ESPECIALIZACIÓN EN EDUCACIÓN MATEMÁTICA PARA BÁSICA PRIMARIA</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>Presencial</t>
+        </is>
+      </c>
+      <c r="I280" t="n">
+        <v>25</v>
+      </c>
+      <c r="J280" t="n">
+        <v>1</v>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr"/>
+      <c r="M280" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="N280" s="2" t="n">
+        <v>42417</v>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>Ciencias de la educación</t>
+        </is>
+      </c>
+      <c r="R280" t="inlineStr">
+        <is>
+          <t>Educación</t>
+        </is>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>Especialización universitaria</t>
+        </is>
+      </c>
+      <c r="T280" t="inlineStr">
+        <is>
+          <t>20/07/2026</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>Inactivo</t>
+        </is>
+      </c>
+      <c r="V280" t="inlineStr">
+        <is>
+          <t>Instituto de Estudios en Educación</t>
         </is>
       </c>
     </row>
